--- a/docs/03_test/従業員登録_テストケース.xlsx
+++ b/docs/03_test/従業員登録_テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05266694-CEB6-4555-948F-F6BEDCEC1346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C77FD6C-3C9D-48E7-BA0F-D8B6D8BD0F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{37CFEBD6-EC7E-401C-904E-EA1D99E4F26F}"/>
   </bookViews>
@@ -150,55 +150,22 @@
     <t>手順</t>
   </si>
   <si>
-    <t>期待結果</t>
-  </si>
-  <si>
     <t>判定</t>
   </si>
   <si>
     <t>日付</t>
   </si>
   <si>
-    <t>名前に空文字を入力し確認ボタンを押す</t>
-  </si>
-  <si>
     <t>〇</t>
   </si>
   <si>
-    <t>名前にaaaaaaaaaaaaaaaaaaaaを入力する</t>
-  </si>
-  <si>
     <t>正常に入力できる</t>
   </si>
   <si>
-    <t>電話番号に1を入力する</t>
-  </si>
-  <si>
     <t>「電話番号の形式が正しくありません」と表示される</t>
   </si>
   <si>
-    <t>電話番号にaを入力する</t>
-  </si>
-  <si>
-    <t>電話番号に090-111-111を入力する</t>
-  </si>
-  <si>
-    <t>電話番号を未入力</t>
-  </si>
-  <si>
-    <t>メールアドレスにaを入力する</t>
-  </si>
-  <si>
     <t>「メールアドレスの形式が正しくありません」と表示される</t>
-  </si>
-  <si>
-    <t>メールアドレスを未入力</t>
-  </si>
-  <si>
-    <t>メールアドレスにtanaka@1.comと入力する</t>
-  </si>
-  <si>
-    <t>所属部署を押すと部署が表示される</t>
   </si>
   <si>
     <t>データベースにある部署が表示される</t>
@@ -263,28 +230,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Fn+F12を押して開発者ツールを開き、maxlengthの値を21に変更する。その後名前にaaaaaaaaaaaaaaaaaaaaaを入力する</t>
-    <rPh sb="7" eb="8">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>カイハツシャ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>アタイ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ゴ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>「氏名は20文字以内で入力してください」と表示される。</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -297,6 +242,90 @@
     <rPh sb="9" eb="11">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待結果(リンクをクリックすることで画面状態を確認できます)</t>
+    <rPh sb="18" eb="22">
+      <t>ガメンジョウタイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の名前にaaaaaaaaaaaaaaaaaaaaを入力する</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面でFn+F12を押して開発者ツールを開き、maxlengthの値を21に変更する。その後名前にaaaaaaaaaaaaaaaaaaaaaを入力する</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクガメン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>カイハツシャ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の氏名に空文字を入力し確認ボタンを押す</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の電話番号に1を入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の電話番号にaを入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の電話番号に090-111-111を入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の電話番号を未入力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面のメールアドレスにaを入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面のメールアドレスを未入力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面のメールアドレスにtanaka@1.comと入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の所属部署を押すと部署が表示される</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -391,7 +420,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -406,6 +435,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -850,7 +882,7 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="9.9140625" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" customWidth="1"/>
+    <col min="3" max="3" width="53.25" customWidth="1"/>
     <col min="4" max="4" width="52.08203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -862,13 +894,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
@@ -876,13 +908,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" s="3">
         <v>46164</v>
@@ -893,13 +925,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="3">
         <v>46164</v>
@@ -910,13 +942,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3">
         <v>46164</v>
@@ -927,13 +959,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="3">
         <v>46164</v>
@@ -944,13 +976,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" s="3">
         <v>46167</v>
@@ -961,13 +993,13 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="3">
         <v>46164</v>
@@ -978,30 +1010,30 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3">
         <v>46164</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="2">
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="3">
         <v>46164</v>
@@ -1012,13 +1044,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3">
         <v>46164</v>
@@ -1028,14 +1060,14 @@
       <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>17</v>
+      <c r="C12" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" s="3">
         <v>46164</v>
@@ -1046,13 +1078,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="3">
         <v>46164</v>
@@ -1063,13 +1095,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" s="3">
         <v>46164</v>
@@ -1080,13 +1112,13 @@
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3">
         <v>46164</v>
@@ -1097,13 +1129,13 @@
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" s="3">
         <v>46164</v>
@@ -1114,13 +1146,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F17" s="3">
         <v>46164</v>
@@ -1131,13 +1163,13 @@
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F18" s="3">
         <v>46164</v>
@@ -1148,13 +1180,13 @@
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F19" s="3">
         <v>46164</v>
@@ -1163,7 +1195,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C12" r:id="rId1" display="mailto:メールアドレスにtanaka@1.com" xr:uid="{FD296BAC-A1FA-4AF8-A832-79F3C9804EAA}"/>
     <hyperlink ref="D3" location="Sheet2!A1" display="「氏名は入力必須です」と表示される" xr:uid="{324B3E6D-BC07-4021-AE8D-0D4376F3A0B5}"/>
     <hyperlink ref="D4" location="Sheet2!A2" display="「氏名は20文字以内で入力してください」と表示される。" xr:uid="{E92F3041-8DFA-4844-B16C-14458B29B4AA}"/>
     <hyperlink ref="D6" location="Sheet2!A3" display="「電話番号の形式が正しくありません」と表示される" xr:uid="{892BEF2C-FF9D-4456-A8A4-1B79E674CE7A}"/>

--- a/docs/03_test/従業員登録_テストケース.xlsx
+++ b/docs/03_test/従業員登録_テストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C77FD6C-3C9D-48E7-BA0F-D8B6D8BD0F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAACE87F-855A-43F6-9C93-341CE94C3151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{37CFEBD6-EC7E-401C-904E-EA1D99E4F26F}"/>
   </bookViews>
@@ -44,7 +44,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="9">
+  <futureMetadata name="XLRICHVALUE" count="13">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -108,8 +108,36 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="9">
+  <valueMetadata count="13">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -136,13 +164,25 @@
     </bk>
     <bk>
       <rc t="1" v="8"/>
+    </bk>
+    <bk>
+      <rc t="1" v="9"/>
+    </bk>
+    <bk>
+      <rc t="1" v="10"/>
+    </bk>
+    <bk>
+      <rc t="1" v="11"/>
+    </bk>
+    <bk>
+      <rc t="1" v="12"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>No</t>
   </si>
@@ -238,13 +278,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>未入力でもエラーが表示されない</t>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>期待結果(リンクをクリックすることで画面状態を確認できます)</t>
     <rPh sb="18" eb="22">
       <t>ガメンジョウタイ</t>
@@ -326,6 +359,60 @@
   </si>
   <si>
     <t>入力画面の所属部署を押すと部署が表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「メールアドレスは入力必須です」と表示される</t>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「電話番号は入力必須です」と表示される</t>
+    <rPh sb="1" eb="5">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>ニュウリョクヒッス</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面の電話番号に090-1111-2222を入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力画面のメールアドレスにsuzuki@example.comを入力する</t>
+    <rPh sb="0" eb="5">
+      <t>ニュウリョ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「同じメールアドレスの従業員が既に存在します。」と表示される</t>
+    <rPh sb="25" eb="27">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「同じ電話番号の従業員が既に存在します。」と表示される</t>
+    <rPh sb="22" eb="24">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -498,7 +585,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="13">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -535,6 +622,22 @@
     <v>8</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>9</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>10</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>11</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>12</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -558,6 +661,10 @@
   <rel r:id="rId7"/>
   <rel r:id="rId8"/>
   <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
+  <rel r:id="rId11"/>
+  <rel r:id="rId12"/>
+  <rel r:id="rId13"/>
 </richValueRels>
 </file>
 
@@ -878,12 +985,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DF60E7-4B77-4E5F-AA8F-19B800E326B2}">
-  <dimension ref="B2:F19"/>
+  <dimension ref="B2:F21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="9.9140625" customWidth="1"/>
     <col min="3" max="3" width="53.25" customWidth="1"/>
-    <col min="4" max="4" width="52.08203125" customWidth="1"/>
+    <col min="4" max="4" width="56.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
@@ -894,7 +1001,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>2</v>
@@ -908,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>20</v>
@@ -925,7 +1032,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>21</v>
@@ -942,7 +1049,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>5</v>
@@ -959,7 +1066,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -976,7 +1083,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>6</v>
@@ -993,27 +1100,23 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
-        <v>46164</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="2">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
@@ -1027,10 +1130,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
@@ -1044,10 +1147,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -1060,11 +1163,11 @@
       <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
@@ -1077,28 +1180,24 @@
       <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>35</v>
+      <c r="C13" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="3">
-        <v>46164</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="2">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>10</v>
+      <c r="C14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
@@ -1107,18 +1206,18 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="34" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="2">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F15" s="3">
         <v>46164</v>
@@ -1129,10 +1228,10 @@
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
@@ -1141,18 +1240,18 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:6" ht="34" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="2">
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3">
         <v>46164</v>
@@ -1163,10 +1262,10 @@
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
@@ -1180,15 +1279,49 @@
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="3">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="2">
         <v>18</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="C20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="2">
         <v>19</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="3">
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3">
         <v>46164</v>
       </c>
     </row>
@@ -1199,14 +1332,18 @@
     <hyperlink ref="D4" location="Sheet2!A2" display="「氏名は20文字以内で入力してください」と表示される。" xr:uid="{E92F3041-8DFA-4844-B16C-14458B29B4AA}"/>
     <hyperlink ref="D6" location="Sheet2!A3" display="「電話番号の形式が正しくありません」と表示される" xr:uid="{892BEF2C-FF9D-4456-A8A4-1B79E674CE7A}"/>
     <hyperlink ref="D7" location="Sheet2!A3" display="「電話番号の形式が正しくありません」と表示される" xr:uid="{E296EEED-184B-4057-8E8C-9CB269F20F35}"/>
-    <hyperlink ref="D10" location="Sheet2!A4" display="「メールアドレスの形式が正しくありません」と表示される" xr:uid="{3CD5B4C7-2E4B-408F-A026-3A2C2315A90C}"/>
-    <hyperlink ref="D13" location="Sheet2!A5" display="データベースにある部署が表示される" xr:uid="{43D369AF-B91C-469C-9345-1D7A3058B8CC}"/>
-    <hyperlink ref="D14" location="Sheet2!A6" display="入力画面に遷移する" xr:uid="{EC96F852-55E5-4F30-BCB9-284F63E8EE73}"/>
-    <hyperlink ref="D15" location="Sheet2!A7" display="確認画面に遷移する" xr:uid="{E3DED5B5-70FC-431B-B7E4-5028EFF9D77D}"/>
-    <hyperlink ref="D16" location="Sheet2!A8" display="完了画面に遷移する" xr:uid="{9CAF2165-D8F9-4C4C-B312-20A54B34AC79}"/>
-    <hyperlink ref="D17" location="Sheet2!A6" display="入力画面に遷移する" xr:uid="{54531332-AFFE-4C08-9B8E-6AE85F906D31}"/>
-    <hyperlink ref="D18" location="Sheet2!A6" display="入力画面に遷移する" xr:uid="{07AE58DD-DBE9-4DE7-8846-F998D2415416}"/>
-    <hyperlink ref="D19" location="Sheet2!A9" display="ホーム画面に遷移する" xr:uid="{D1B178DE-8D6E-4C9C-8931-AC8107E69305}"/>
+    <hyperlink ref="D11" location="Sheet2!A4" display="「メールアドレスの形式が正しくありません」と表示される" xr:uid="{3CD5B4C7-2E4B-408F-A026-3A2C2315A90C}"/>
+    <hyperlink ref="D15" location="Sheet2!A5" display="データベースにある部署が表示される" xr:uid="{43D369AF-B91C-469C-9345-1D7A3058B8CC}"/>
+    <hyperlink ref="D16" location="Sheet2!A6" display="入力画面に遷移する" xr:uid="{EC96F852-55E5-4F30-BCB9-284F63E8EE73}"/>
+    <hyperlink ref="D17" location="Sheet2!A7" display="確認画面に遷移する" xr:uid="{E3DED5B5-70FC-431B-B7E4-5028EFF9D77D}"/>
+    <hyperlink ref="D18" location="Sheet2!A8" display="完了画面に遷移する" xr:uid="{9CAF2165-D8F9-4C4C-B312-20A54B34AC79}"/>
+    <hyperlink ref="D19" location="Sheet2!A6" display="入力画面に遷移する" xr:uid="{54531332-AFFE-4C08-9B8E-6AE85F906D31}"/>
+    <hyperlink ref="D20" location="Sheet2!A6" display="入力画面に遷移する" xr:uid="{07AE58DD-DBE9-4DE7-8846-F998D2415416}"/>
+    <hyperlink ref="D21" location="Sheet2!A9" display="ホーム画面に遷移する" xr:uid="{D1B178DE-8D6E-4C9C-8931-AC8107E69305}"/>
+    <hyperlink ref="D8" location="Sheet2!A10" display="「同じ電話番号の従業員が既に存在します。」と表示される" xr:uid="{7B6F8C3C-71D4-4749-B746-215FF434AA9E}"/>
+    <hyperlink ref="D13" location="Sheet2!A11" display="「同じメールアドレスの従業員が既に存在します。」と表示される" xr:uid="{5F8BE0BB-DA26-4383-8CBA-8BD41599300A}"/>
+    <hyperlink ref="D10" location="Sheet2!A12" display="「電話番号は入力必須です」と表示される" xr:uid="{5A541CBC-1190-487B-A67C-73937F5361A8}"/>
+    <hyperlink ref="D12" location="Sheet2!A13" display="「メールアドレスは入力必須です」と表示される" xr:uid="{543C1CD2-F749-4700-9BEA-B9145D064289}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1214,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B91EC7E6-6A79-49BC-84A7-88D984ECE092}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="47.5" customWidth="1"/>
@@ -1265,6 +1402,26 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="10" spans="1:1" ht="100" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="103" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="78" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="84.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
